--- a/NEW BOT 02/MEP_BOM_Master_Report.xlsx
+++ b/NEW BOT 02/MEP_BOM_Master_Report.xlsx
@@ -797,7 +797,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data Source: MEP Group ERP  |  Report Generated: 19-Sep-2026 03:20 PM</t>
+          <t>Data Source: MEP Group ERP  |  Report Generated: 21-Sep-2026 09:42 AM</t>
         </is>
       </c>
     </row>
